--- a/claude-with-tools/plots/python_cost.xlsx
+++ b/claude-with-tools/plots/python_cost.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/emmayu/Desktop/llm-with-tools/claude-with-tools/plots/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{165D0218-865A-664E-8143-12CF448E1BD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2E3076B-1B9C-C94A-8292-6C37C6983742}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1900" yWindow="1820" windowWidth="27240" windowHeight="16440" activeTab="4" xr2:uid="{9435413A-D49A-EB49-A825-082284DA3D2B}"/>
   </bookViews>
@@ -468,10 +468,16 @@
       <c r="A5" s="1" t="s">
         <v>2</v>
       </c>
+      <c r="B5">
+        <v>0.39930474999999999</v>
+      </c>
     </row>
     <row r="6" spans="1:2" ht="29">
       <c r="A6" s="1" t="s">
         <v>3</v>
+      </c>
+      <c r="B6">
+        <v>0.28579399999999999</v>
       </c>
     </row>
   </sheetData>
@@ -501,10 +507,16 @@
       <c r="A5" s="1" t="s">
         <v>2</v>
       </c>
+      <c r="B5">
+        <v>0.57272249999999902</v>
+      </c>
     </row>
     <row r="6" spans="1:2" ht="29">
       <c r="A6" s="1" t="s">
         <v>3</v>
+      </c>
+      <c r="B6">
+        <v>0.3711525</v>
       </c>
     </row>
   </sheetData>
@@ -534,10 +546,16 @@
       <c r="A5" s="1" t="s">
         <v>2</v>
       </c>
+      <c r="B5">
+        <v>0.94179625</v>
+      </c>
     </row>
     <row r="6" spans="1:2" ht="29">
       <c r="A6" s="1" t="s">
         <v>3</v>
+      </c>
+      <c r="B6">
+        <v>0.65326474999999995</v>
       </c>
     </row>
   </sheetData>
@@ -567,10 +585,16 @@
       <c r="A5" s="1" t="s">
         <v>2</v>
       </c>
+      <c r="B5">
+        <v>0.46516774999999999</v>
+      </c>
     </row>
     <row r="6" spans="1:2" ht="29">
       <c r="A6" s="1" t="s">
         <v>3</v>
+      </c>
+      <c r="B6">
+        <v>0.30333399999999999</v>
       </c>
     </row>
   </sheetData>
@@ -600,10 +624,16 @@
       <c r="A5" s="1" t="s">
         <v>2</v>
       </c>
+      <c r="B5">
+        <v>0.51242374999999996</v>
+      </c>
     </row>
     <row r="6" spans="1:2" ht="29">
       <c r="A6" s="1" t="s">
         <v>3</v>
+      </c>
+      <c r="B6">
+        <v>1.4449179999999999</v>
       </c>
     </row>
   </sheetData>
